--- a/file_downloads/Energy Trading Optimization - March 2026.xlsx
+++ b/file_downloads/Energy Trading Optimization - March 2026.xlsx
@@ -723,7 +723,7 @@
         <is>
           <t>4000.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -740,7 +740,7 @@
         <is>
           <t>4640.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -772,14 +772,14 @@
         <is>
           <t>1950.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
           <t>1999.20
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
@@ -801,7 +801,7 @@
         <is>
           <t>9000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="T4" s="4" t="inlineStr">
@@ -813,21 +813,21 @@
         <is>
           <t>7800.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
           <t>9000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="W4" s="6" t="inlineStr">
         <is>
           <t>8849.05
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="X4" s="4" t="inlineStr">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="Z4" s="7" t="n">
-        <v>668896.875</v>
+        <v>90301.078125</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
@@ -869,14 +869,14 @@
         <is>
           <t>5450.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
           <t>5600.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -893,14 +893,14 @@
         <is>
           <t>11000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
           <t>6969.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -922,14 +922,14 @@
         <is>
           <t>2750.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
           <t>2349.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr">
@@ -951,14 +951,14 @@
         <is>
           <t>14299.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
           <t>13789.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="U5" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="Z5" s="7" t="n">
-        <v>1339885</v>
+        <v>180884.4749999999</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
@@ -1015,14 +1015,14 @@
         <is>
           <t>3051.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
           <t>3100.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -1034,28 +1034,28 @@
         <is>
           <t>5800.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>4185.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
           <t>5450.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
           <t>5000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -1072,14 +1072,14 @@
         <is>
           <t>2490.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
           <t>2749.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
@@ -1111,14 +1111,14 @@
         <is>
           <t>9000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
           <t>7947.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="W6" s="4" t="inlineStr">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="Z6" s="7" t="n">
-        <v>759170</v>
+        <v>102487.95</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
@@ -1165,14 +1165,14 @@
         <is>
           <t>3600.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
           <t>3600.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1189,14 +1189,14 @@
         <is>
           <t>9899.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
           <t>7500.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1218,14 +1218,14 @@
         <is>
           <t>1500.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
           <t>1500.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
@@ -1252,14 +1252,14 @@
         <is>
           <t>10000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
         <is>
           <t>10999.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="Z7" s="7" t="n">
-        <v>1288405</v>
+        <v>173934.675</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
@@ -1311,14 +1311,14 @@
         <is>
           <t>3300.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
           <t>3300.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -1330,14 +1330,14 @@
         <is>
           <t>5880.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
           <t>10264.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1364,14 +1364,14 @@
         <is>
           <t>850.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
           <t>850.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
@@ -1398,14 +1398,14 @@
         <is>
           <t>13499.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
         <is>
           <t>13499.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V8" s="4" t="inlineStr">
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="Z8" s="7" t="n">
-        <v>1613495</v>
+        <v>217821.825</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
@@ -1457,14 +1457,14 @@
         <is>
           <t>2799.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
           <t>2800.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1481,14 +1481,14 @@
         <is>
           <t>10150.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
           <t>9200.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1505,14 +1505,14 @@
         <is>
           <t>999.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
           <t>999.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1544,14 +1544,14 @@
         <is>
           <t>11500.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
         <is>
           <t>13000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V9" s="4" t="inlineStr">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="Z9" s="7" t="n">
-        <v>1684032.5</v>
+        <v>227344.3875</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
@@ -1603,7 +1603,7 @@
         <is>
           <t>5800.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1620,21 +1620,21 @@
         <is>
           <t>5900.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
           <t>7134.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
           <t>6991.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -1651,14 +1651,14 @@
         <is>
           <t>450.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
           <t>198.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -1690,14 +1690,14 @@
         <is>
           <t>14577.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
         <is>
           <t>14577.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="Z10" s="7" t="n">
-        <v>1407482.5</v>
+        <v>190010.1375</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
@@ -1759,7 +1759,7 @@
         <is>
           <t>5800.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1771,21 +1771,21 @@
         <is>
           <t>5000.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
           <t>9200.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
           <t>9500.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1802,14 +1802,14 @@
         <is>
           <t>1500.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
           <t>1500.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
@@ -1841,14 +1841,14 @@
         <is>
           <t>15000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
           <t>15000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="Z11" s="7" t="n">
-        <v>1588750</v>
+        <v>214481.25</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
@@ -1890,14 +1890,14 @@
         <is>
           <t>5800.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
           <t>5800.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1919,14 +1919,14 @@
         <is>
           <t>13000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
           <t>12675.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
@@ -1953,14 +1953,14 @@
         <is>
           <t>1250.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P12" s="5" t="inlineStr">
         <is>
           <t>1250.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
@@ -1982,14 +1982,14 @@
         <is>
           <t>15000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
         <is>
           <t>15000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V12" s="4" t="inlineStr">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="Z12" s="7" t="n">
-        <v>1904312.5</v>
+        <v>257082.1875</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
@@ -2041,14 +2041,14 @@
         <is>
           <t>4850.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
           <t>5800.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -2065,14 +2065,14 @@
         <is>
           <t>13000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
           <t>9300.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -2099,14 +2099,14 @@
         <is>
           <t>1200.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P13" s="5" t="inlineStr">
         <is>
           <t>1000.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
@@ -2133,14 +2133,14 @@
         <is>
           <t>14587.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
           <t>14587.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
@@ -2152,18 +2152,18 @@
         <is>
           <t>6000.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="Y13" s="6" t="inlineStr">
         <is>
           <t>7183.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="Z13" s="7" t="n">
-        <v>1796582.5</v>
+        <v>242538.6375</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
@@ -2191,14 +2191,14 @@
         <is>
           <t>4850.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
           <t>5104.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -2210,14 +2210,14 @@
         <is>
           <t>8499.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
           <t>11000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -2249,14 +2249,14 @@
         <is>
           <t>1200.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P14" s="5" t="inlineStr">
         <is>
           <t>1200.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
@@ -2278,14 +2278,14 @@
         <is>
           <t>14587.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="U14" s="6" t="inlineStr">
         <is>
           <t>14897.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V14" s="4" t="inlineStr">
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Z14" s="7" t="n">
-        <v>1678107.5</v>
+        <v>226544.5125</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
@@ -2332,14 +2332,14 @@
         <is>
           <t>3500.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
           <t>3899.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -2356,14 +2356,14 @@
         <is>
           <t>13467.05
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
           <t>14580.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -2390,14 +2390,14 @@
         <is>
           <t>477.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
           <t>477.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
@@ -2424,14 +2424,14 @@
         <is>
           <t>15000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="U15" s="6" t="inlineStr">
         <is>
           <t>15000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Z15" s="7" t="n">
-        <v>2318702.375</v>
+        <v>313024.8206250001</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
@@ -2478,14 +2478,14 @@
         <is>
           <t>2600.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
           <t>2600.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -2502,14 +2502,14 @@
         <is>
           <t>6500.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
           <t>10966.98
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -2536,14 +2536,14 @@
         <is>
           <t>350.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
           <t>300.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
@@ -2570,14 +2570,14 @@
         <is>
           <t>15000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="U16" s="6" t="inlineStr">
         <is>
           <t>14798.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V16" s="4" t="inlineStr">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Z16" s="7" t="n">
-        <v>1937961.55</v>
+        <v>261624.80925</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
@@ -2614,14 +2614,14 @@
         <is>
           <t>5150.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
           <t>6180.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -2633,14 +2633,14 @@
         <is>
           <t>4000.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
           <t>2800.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -2652,7 +2652,7 @@
         <is>
           <t>5600.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -2664,7 +2664,7 @@
         <is>
           <t>6206.62
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -2681,28 +2681,28 @@
         <is>
           <t>373.50
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
           <t>501.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
           <t>638.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P17" s="5" t="inlineStr">
         <is>
           <t>431.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="Q17" s="4" t="inlineStr">
@@ -2724,14 +2724,14 @@
         <is>
           <t>13900.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="U17" s="6" t="inlineStr">
         <is>
           <t>14498.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V17" s="4" t="inlineStr">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="Z17" s="7" t="n">
-        <v>1537660.7</v>
+        <v>207584.1945</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
@@ -2778,7 +2778,7 @@
         <is>
           <t>5000.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -2790,21 +2790,21 @@
         <is>
           <t>5000.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
           <t>6399.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
           <t>6390.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -2841,14 +2841,14 @@
         <is>
           <t>899.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P18" s="5" t="inlineStr">
         <is>
           <t>894.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="Q18" s="4" t="inlineStr">
@@ -2875,14 +2875,14 @@
         <is>
           <t>10349.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
           <t>10349.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="Z18" s="7" t="n">
-        <v>971500</v>
+        <v>131152.5</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
@@ -2914,28 +2914,28 @@
         <is>
           <t>3300.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
           <t>4185.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
           <t>3000.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
           <t>3000.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -2957,14 +2957,14 @@
         <is>
           <t>10966.98
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
           <t>8349.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -2981,14 +2981,14 @@
         <is>
           <t>1982.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
           <t>1400.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -3020,14 +3020,14 @@
         <is>
           <t>14990.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="U19" s="6" t="inlineStr">
         <is>
           <t>14990.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V19" s="4" t="inlineStr">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="Z19" s="7" t="n">
-        <v>1874541.55</v>
+        <v>253063.10925</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
@@ -3064,28 +3064,28 @@
         <is>
           <t>4700.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
           <t>7850.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
           <t>6990.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
           <t>6990.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -3102,7 +3102,7 @@
         <is>
           <t>15000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -3114,7 +3114,7 @@
         <is>
           <t>15000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -3126,7 +3126,7 @@
         <is>
           <t>4000.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -3138,7 +3138,7 @@
         <is>
           <t>4300.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -3165,7 +3165,7 @@
         <is>
           <t>14990.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="T20" s="4" t="inlineStr">
@@ -3177,7 +3177,7 @@
         <is>
           <t>14899.99
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="Z20" s="7" t="n">
-        <v>1801199.525</v>
+        <v>243161.935875</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
@@ -3224,14 +3224,14 @@
         <is>
           <t>3100.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
           <t>3100.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -3258,14 +3258,14 @@
         <is>
           <t>7999.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
           <t>7966.99
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -3282,14 +3282,14 @@
         <is>
           <t>2800.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
           <t>2560.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
@@ -3321,14 +3321,14 @@
         <is>
           <t>14990.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
           <t>14902.93
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="Z21" s="7" t="n">
-        <v>1571398.7</v>
+        <v>212138.8245</v>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
@@ -3370,14 +3370,14 @@
         <is>
           <t>4300.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
           <t>4000.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -3399,14 +3399,14 @@
         <is>
           <t>13500.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
           <t>12967.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -3428,7 +3428,7 @@
         <is>
           <t>3795.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
@@ -3440,7 +3440,7 @@
         <is>
           <t>5000.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="Q22" s="4" t="inlineStr">
@@ -3462,14 +3462,14 @@
         <is>
           <t>14990.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="U22" s="6" t="inlineStr">
         <is>
           <t>14990.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V22" s="4" t="inlineStr">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="Z22" s="7" t="n">
-        <v>1783745</v>
+        <v>240805.575</v>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
@@ -3516,14 +3516,14 @@
         <is>
           <t>4800.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
           <t>4300.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -3545,14 +3545,14 @@
         <is>
           <t>10529.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
           <t>8299.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -3564,28 +3564,28 @@
         <is>
           <t>2499.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
           <t>2999.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
           <t>1999.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
           <t>2499.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
@@ -3612,14 +3612,14 @@
         <is>
           <t>14901.35
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="U23" s="6" t="inlineStr">
         <is>
           <t>14936.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V23" s="4" t="inlineStr">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="Z23" s="7" t="n">
-        <v>1608964.125</v>
+        <v>217210.156875</v>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
@@ -3671,14 +3671,14 @@
         <is>
           <t>5100.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
           <t>5100.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -3690,14 +3690,14 @@
         <is>
           <t>7300.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
           <t>7464.50
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -3729,14 +3729,14 @@
         <is>
           <t>1549.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P24" s="5" t="inlineStr">
         <is>
           <t>1792.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="Q24" s="4" t="inlineStr">
@@ -3758,7 +3758,7 @@
         <is>
           <t>14999.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="U24" s="4" t="inlineStr">
@@ -3770,7 +3770,7 @@
         <is>
           <t>14976.41
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="Z24" s="7" t="n">
-        <v>1414243.225</v>
+        <v>190922.835375</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
@@ -3862,14 +3862,14 @@
         <is>
           <t>880.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
           <t>846.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -3896,7 +3896,7 @@
         <is>
           <t>14978.01
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="U25" s="4" t="inlineStr">
@@ -3913,7 +3913,7 @@
         <is>
           <t>14976.95
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="X25" s="4" t="inlineStr">
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="Z25" s="7" t="n">
-        <v>1332245.6</v>
+        <v>179853.156</v>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
@@ -3945,7 +3945,7 @@
         <is>
           <t>6500.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -3957,7 +3957,7 @@
         <is>
           <t>6504.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -3974,14 +3974,14 @@
         <is>
           <t>14791.66
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
           <t>13967.04
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -4008,14 +4008,14 @@
         <is>
           <t>4300.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
           <t>5167.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
@@ -4037,14 +4037,14 @@
         <is>
           <t>15000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
           <t>15000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr">
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="Z26" s="7" t="n">
-        <v>1611310.75</v>
+        <v>217526.95125</v>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
@@ -4086,14 +4086,14 @@
         <is>
           <t>6500.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
           <t>7211.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -4110,14 +4110,14 @@
         <is>
           <t>4200.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
           <t>5500.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -4129,14 +4129,14 @@
         <is>
           <t>9767.01
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
           <t>8292.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -4158,14 +4158,14 @@
         <is>
           <t>1600.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
         <is>
           <t>2265.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
@@ -4197,14 +4197,14 @@
         <is>
           <t>15000.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V27" s="6" t="inlineStr">
         <is>
           <t>14979.69
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="Z27" s="7" t="n">
-        <v>1570948.25</v>
+        <v>212078.01375</v>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
@@ -4251,14 +4251,14 @@
         <is>
           <t>4200.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
           <t>4200.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -4270,14 +4270,14 @@
         <is>
           <t>6699.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
           <t>7767.03
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -4304,14 +4304,14 @@
         <is>
           <t>1000.01
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
           <t>1300.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
@@ -4328,14 +4328,14 @@
         <is>
           <t>14972.10
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
           <t>9000.00
 BUY
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="T28" s="4" t="inlineStr">
@@ -4347,14 +4347,14 @@
         <is>
           <t>14969.70
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="V28" s="6" t="inlineStr">
         <is>
           <t>13500.00
 SELL
-50.00MWh</t>
+6.75MWh</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="Z28" s="7" t="n">
-        <v>1716371.4</v>
+        <v>231710.139</v>
       </c>
     </row>
     <row r="31">
